--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -39,37 +39,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,529 +171,451 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1946,7 +1946,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -1961,40 +1961,40 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="6">
         <v>9.47</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="2">
         <v>10.08</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="7">
         <v>11.01</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="3">
         <v>17.07</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="4">
         <v>17.23</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="13">
         <v>17.15</v>
       </c>
       <c r="O2" s="8">
         <v>11.95</v>
       </c>
-      <c r="P2" s="12">
+      <c r="P2" s="9">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="9">
+      <c r="Q2" s="10">
         <v>8.74</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="11">
         <v>8</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="1">
         <v>8.53</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="5">
         <v>-13.61</v>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="18" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2023,40 +2023,40 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="19">
+      <c r="I3" s="20">
         <v>17.6</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="16">
         <v>15.99</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="21">
         <v>12.85</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="24">
         <v>9.36</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="22">
         <v>8.73</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="25">
         <v>8.15</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="17">
         <v>6.67</v>
       </c>
-      <c r="P3" s="25">
+      <c r="P3" s="19">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="26">
         <v>1.21</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="14">
         <v>0.49</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="15">
         <v>2.02</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="23">
         <v>-15.72</v>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2088,37 +2088,37 @@
       <c r="I4" s="35">
         <v>0</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="37">
         <v>16.09</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="27">
         <v>35.27</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="32">
         <v>27.54</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="33">
         <v>14.04</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="28">
         <v>14.69</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="29">
         <v>0.26</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="30">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="36">
         <v>8.86</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="31">
         <v>11.7</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="34">
         <v>17.14</v>
       </c>
-      <c r="T4" s="34">
+      <c r="T4" s="38">
         <v>-3.33</v>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       <c r="C5" t="str">
         <v>600103</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="45" t="str">
         <v>净卖: -2325.72万</v>
       </c>
       <c r="E5">
@@ -2147,40 +2147,40 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="46">
         <v>7.58</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="42">
         <v>8.75</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="47">
         <v>7.87</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="51">
         <v>5.25</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="43">
         <v>5.83</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="44">
         <v>8.16</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="48">
         <v>10.5</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="52">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="49">
         <v>2.62</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="40">
         <v>4.37</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="50">
         <v>10.5</v>
       </c>
-      <c r="T5" s="51">
+      <c r="T5" s="41">
         <v>25.36</v>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2209,40 +2209,40 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="58">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="62">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="64">
         <v>-13.5</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="63">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="55">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="65">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="56">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="59">
         <v>-18.6</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="57">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="53">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="62">
+      <c r="T6" s="54">
         <v>11.62</v>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2271,22 +2271,22 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="67">
         <v>2.3</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="68">
         <v>6.39</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="69">
         <v>2.05</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="70">
         <v>3.84</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="71">
         <v>9.97</v>
       </c>
       <c r="O7" t="str"/>
@@ -2294,7 +2294,7 @@
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="67">
+      <c r="T7" s="72">
         <v>9.97</v>
       </c>
     </row>
@@ -2357,40 +2357,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="76">
+      <c r="I9" s="77">
         <v>50</v>
       </c>
-      <c r="J9" s="80">
+      <c r="J9" s="78">
         <v>83.33</v>
       </c>
-      <c r="K9" s="74">
+      <c r="K9" s="83">
         <v>83.33</v>
       </c>
-      <c r="L9" s="77">
+      <c r="L9" s="79">
         <v>83.33</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="74">
         <v>83.33</v>
       </c>
-      <c r="N9" s="84">
+      <c r="N9" s="80">
         <v>83.33</v>
       </c>
-      <c r="O9" s="79">
+      <c r="O9" s="84">
         <v>80</v>
       </c>
-      <c r="P9" s="81">
+      <c r="P9" s="82">
         <v>80</v>
       </c>
-      <c r="Q9" s="85">
+      <c r="Q9" s="75">
         <v>80</v>
       </c>
-      <c r="R9" s="75">
+      <c r="R9" s="85">
         <v>80</v>
       </c>
-      <c r="S9" s="82">
+      <c r="S9" s="76">
         <v>80</v>
       </c>
-      <c r="T9" s="83">
+      <c r="T9" s="81">
         <v>50</v>
       </c>
     </row>
@@ -2405,40 +2405,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="86">
+      <c r="I10" s="87">
         <v>5.78</v>
       </c>
-      <c r="J10" s="94">
+      <c r="J10" s="93">
         <v>6.97</v>
       </c>
       <c r="K10" s="95">
         <v>10.45</v>
       </c>
-      <c r="L10" s="90">
+      <c r="L10" s="88">
         <v>7.96</v>
       </c>
-      <c r="M10" s="87">
+      <c r="M10" s="96">
         <v>5.87</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N10" s="94">
         <v>7.06</v>
       </c>
-      <c r="O10" s="91">
+      <c r="O10" s="90">
         <v>2.95</v>
       </c>
-      <c r="P10" s="92">
+      <c r="P10" s="91">
         <v>1.65</v>
       </c>
-      <c r="Q10" s="96">
+      <c r="Q10" s="92">
         <v>0.57</v>
       </c>
-      <c r="R10" s="88">
+      <c r="R10" s="89">
         <v>1.12</v>
       </c>
-      <c r="S10" s="93">
+      <c r="S10" s="97">
         <v>3.2</v>
       </c>
-      <c r="T10" s="89">
+      <c r="T10" s="86">
         <v>2.38</v>
       </c>
     </row>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -39,25 +39,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB62431"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFBEBEC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,25 +129,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,445 +183,427 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FC483"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -550,72 +616,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1946,7 +1946,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -1961,13 +1961,13 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="2">
         <v>9.47</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="12">
         <v>10.08</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="10">
         <v>11.01</v>
       </c>
       <c r="L2" s="3">
@@ -1976,25 +1976,25 @@
       <c r="M2" s="4">
         <v>17.23</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="5">
         <v>17.15</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="6">
         <v>11.95</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="8">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="11">
         <v>8.74</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="9">
         <v>8</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="13">
         <v>8.53</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="7">
         <v>-13.61</v>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2023,40 +2023,40 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="25">
         <v>17.6</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="19">
         <v>15.99</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="23">
         <v>12.85</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="16">
         <v>9.36</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="24">
         <v>8.73</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="20">
         <v>8.15</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="21">
         <v>6.67</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="26">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="17">
         <v>1.21</v>
       </c>
       <c r="R3" s="14">
         <v>0.49</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="18">
         <v>2.02</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="15">
         <v>-15.72</v>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2085,40 +2085,40 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="37">
         <v>0</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="34">
         <v>16.09</v>
       </c>
-      <c r="K4" s="27">
+      <c r="K4" s="39">
         <v>35.27</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="27">
         <v>27.54</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="31">
         <v>14.04</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="38">
         <v>14.69</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="28">
         <v>0.26</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="35">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="29">
         <v>8.86</v>
       </c>
-      <c r="R4" s="31">
+      <c r="R4" s="36">
         <v>11.7</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="32">
         <v>17.14</v>
       </c>
-      <c r="T4" s="38">
+      <c r="T4" s="30">
         <v>-3.33</v>
       </c>
     </row>
@@ -2150,37 +2150,37 @@
       <c r="I5" s="46">
         <v>7.58</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="52">
         <v>8.75</v>
       </c>
       <c r="K5" s="47">
         <v>7.87</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="40">
         <v>5.25</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="48">
         <v>5.83</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="41">
         <v>8.16</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="49">
         <v>10.5</v>
       </c>
-      <c r="P5" s="52">
+      <c r="P5" s="50">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="42">
         <v>2.62</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="43">
         <v>4.37</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="51">
         <v>10.5</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="44">
         <v>25.36</v>
       </c>
     </row>
@@ -2194,7 +2194,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2209,40 +2209,40 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="54">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="60">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="55">
         <v>-13.5</v>
       </c>
       <c r="M6" s="63">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="64">
         <v>-15.75</v>
       </c>
       <c r="O6" s="65">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="56">
+      <c r="P6" s="53">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="56">
         <v>-18.6</v>
       </c>
       <c r="R6" s="57">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="58">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="61">
         <v>11.62</v>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2271,22 +2271,22 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="68">
         <v>0</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="69">
         <v>2.3</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="70">
         <v>6.39</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="71">
         <v>2.05</v>
       </c>
-      <c r="M7" s="70">
+      <c r="M7" s="72">
         <v>3.84</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="73">
         <v>9.97</v>
       </c>
       <c r="O7" t="str"/>
@@ -2294,7 +2294,7 @@
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="72">
+      <c r="T7" s="66">
         <v>9.97</v>
       </c>
     </row>
@@ -2357,40 +2357,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="77">
+      <c r="I9" s="75">
         <v>50</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="84">
         <v>83.33</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="81">
         <v>83.33</v>
       </c>
-      <c r="L9" s="79">
+      <c r="L9" s="82">
         <v>83.33</v>
       </c>
-      <c r="M9" s="74">
+      <c r="M9" s="76">
         <v>83.33</v>
       </c>
-      <c r="N9" s="80">
+      <c r="N9" s="85">
         <v>83.33</v>
       </c>
-      <c r="O9" s="84">
+      <c r="O9" s="74">
         <v>80</v>
       </c>
-      <c r="P9" s="82">
+      <c r="P9" s="80">
         <v>80</v>
       </c>
-      <c r="Q9" s="75">
+      <c r="Q9" s="77">
         <v>80</v>
       </c>
-      <c r="R9" s="85">
+      <c r="R9" s="78">
         <v>80</v>
       </c>
-      <c r="S9" s="76">
+      <c r="S9" s="79">
         <v>80</v>
       </c>
-      <c r="T9" s="81">
+      <c r="T9" s="83">
         <v>50</v>
       </c>
     </row>
@@ -2405,40 +2405,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="87">
+      <c r="I10" s="92">
         <v>5.78</v>
       </c>
-      <c r="J10" s="93">
+      <c r="J10" s="86">
         <v>6.97</v>
       </c>
-      <c r="K10" s="95">
+      <c r="K10" s="96">
         <v>10.45</v>
       </c>
-      <c r="L10" s="88">
+      <c r="L10" s="87">
         <v>7.96</v>
       </c>
-      <c r="M10" s="96">
+      <c r="M10" s="88">
         <v>5.87</v>
       </c>
-      <c r="N10" s="94">
+      <c r="N10" s="93">
         <v>7.06</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="94">
         <v>2.95</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="89">
         <v>1.65</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="Q10" s="90">
         <v>0.57</v>
       </c>
-      <c r="R10" s="89">
+      <c r="R10" s="95">
         <v>1.12</v>
       </c>
-      <c r="S10" s="97">
+      <c r="S10" s="91">
         <v>3.2</v>
       </c>
-      <c r="T10" s="86">
+      <c r="T10" s="97">
         <v>2.38</v>
       </c>
     </row>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="99">
+  <fills count="100">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,25 +39,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,7 +189,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6AC27E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C5C9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,528 +621,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6FC483"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="98">
+  <borders count="99">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1311,7 +1324,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1602,6 +1615,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="97" fillId="98" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="98" fillId="99" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1946,7 +1962,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -1961,41 +1977,41 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="13">
         <v>9.47</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="3">
         <v>10.08</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>11.01</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
         <v>17.07</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="2">
         <v>17.23</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="4">
         <v>17.15</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="12">
         <v>11.95</v>
       </c>
-      <c r="P2" s="8">
+      <c r="P2" s="5">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="11">
+      <c r="Q2" s="10">
         <v>8.74</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="6">
         <v>8</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="11">
         <v>8.53</v>
       </c>
       <c r="T2" s="7">
-        <v>-13.61</v>
+        <v>-12.68</v>
       </c>
     </row>
     <row r="3">
@@ -2008,7 +2024,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="26" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2023,41 +2039,41 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="23">
         <v>17.6</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="24">
         <v>15.99</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="16">
         <v>12.85</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="20">
         <v>9.36</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="21">
         <v>8.73</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="14">
         <v>8.15</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="15">
         <v>6.67</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="17">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="18">
         <v>1.21</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="22">
         <v>0.49</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="19">
         <v>2.02</v>
       </c>
-      <c r="T3" s="15">
-        <v>-15.72</v>
+      <c r="T3" s="25">
+        <v>-15.49</v>
       </c>
     </row>
     <row r="4">
@@ -2070,7 +2086,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2085,41 +2101,41 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="38">
         <v>0</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="29">
         <v>16.09</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="30">
         <v>35.27</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="31">
         <v>27.54</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="34">
         <v>14.04</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="39">
         <v>14.69</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <v>0.26</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="32">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="29">
+      <c r="Q4" s="28">
         <v>8.86</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="33">
         <v>11.7</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="35">
         <v>17.14</v>
       </c>
-      <c r="T4" s="30">
-        <v>-3.33</v>
+      <c r="T4" s="36">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="5">
@@ -2147,41 +2163,41 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="42">
         <v>7.58</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="46">
         <v>8.75</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="43">
         <v>7.87</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="52">
         <v>5.25</v>
       </c>
-      <c r="M5" s="48">
+      <c r="M5" s="51">
         <v>5.83</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="40">
         <v>8.16</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="47">
         <v>10.5</v>
       </c>
-      <c r="P5" s="50">
+      <c r="P5" s="48">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="41">
         <v>2.62</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="49">
         <v>4.37</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="50">
         <v>10.5</v>
       </c>
       <c r="T5" s="44">
-        <v>25.36</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="6">
@@ -2194,7 +2210,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2209,16 +2225,16 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="56">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="61">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="54">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="62">
         <v>-13.5</v>
       </c>
       <c r="M6" s="63">
@@ -2227,23 +2243,23 @@
       <c r="N6" s="64">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="55">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="65">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="58">
         <v>-18.6</v>
       </c>
-      <c r="R6" s="57">
+      <c r="R6" s="59">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="53">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="61">
-        <v>11.62</v>
+      <c r="T6" s="57">
+        <v>18.41</v>
       </c>
     </row>
     <row r="7">
@@ -2256,7 +2272,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2271,31 +2287,33 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="73">
         <v>0</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="67">
         <v>2.3</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="68">
         <v>6.39</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="74">
         <v>2.05</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="69">
         <v>3.84</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="71">
         <v>9.97</v>
       </c>
-      <c r="O7" t="str"/>
+      <c r="O7" s="66">
+        <v>20.97</v>
+      </c>
       <c r="P7" t="str"/>
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="66">
-        <v>9.97</v>
+      <c r="T7" s="72">
+        <v>20.97</v>
       </c>
     </row>
     <row r="8">
@@ -2328,7 +2346,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>5</v>
@@ -2357,40 +2375,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="75">
+      <c r="I9" s="85">
         <v>50</v>
       </c>
-      <c r="J9" s="84">
+      <c r="J9" s="82">
         <v>83.33</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="86">
         <v>83.33</v>
       </c>
-      <c r="L9" s="82">
+      <c r="L9" s="75">
         <v>83.33</v>
       </c>
-      <c r="M9" s="76">
+      <c r="M9" s="78">
         <v>83.33</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="76">
         <v>83.33</v>
       </c>
-      <c r="O9" s="74">
+      <c r="O9" s="81">
+        <v>83.33</v>
+      </c>
+      <c r="P9" s="83">
         <v>80</v>
       </c>
-      <c r="P9" s="80">
+      <c r="Q9" s="79">
         <v>80</v>
       </c>
-      <c r="Q9" s="77">
+      <c r="R9" s="77">
         <v>80</v>
       </c>
-      <c r="R9" s="78">
+      <c r="S9" s="84">
         <v>80</v>
       </c>
-      <c r="S9" s="79">
-        <v>80</v>
-      </c>
-      <c r="T9" s="83">
+      <c r="T9" s="80">
         <v>50</v>
       </c>
     </row>
@@ -2405,41 +2423,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="92">
+      <c r="I10" s="97">
         <v>5.78</v>
       </c>
-      <c r="J10" s="86">
+      <c r="J10" s="87">
         <v>6.97</v>
       </c>
-      <c r="K10" s="96">
+      <c r="K10" s="90">
         <v>10.45</v>
       </c>
-      <c r="L10" s="87">
+      <c r="L10" s="94">
         <v>7.96</v>
       </c>
-      <c r="M10" s="88">
+      <c r="M10" s="95">
         <v>5.87</v>
       </c>
-      <c r="N10" s="93">
+      <c r="N10" s="98">
         <v>7.06</v>
       </c>
-      <c r="O10" s="94">
-        <v>2.95</v>
-      </c>
-      <c r="P10" s="89">
+      <c r="O10" s="91">
+        <v>5.95</v>
+      </c>
+      <c r="P10" s="92">
         <v>1.65</v>
       </c>
-      <c r="Q10" s="90">
+      <c r="Q10" s="88">
         <v>0.57</v>
       </c>
-      <c r="R10" s="95">
+      <c r="R10" s="89">
         <v>1.12</v>
       </c>
-      <c r="S10" s="91">
+      <c r="S10" s="96">
         <v>3.2</v>
       </c>
-      <c r="T10" s="97">
-        <v>2.38</v>
+      <c r="T10" s="93">
+        <v>7.61</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="100">
+  <fills count="101">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -57,6 +57,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -69,481 +99,517 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6AC27E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -565,68 +631,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="99">
+  <borders count="100">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1324,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1618,6 +1631,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="98" fillId="99" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="99" fillId="100" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1962,7 +1978,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -1977,41 +1993,41 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="7">
         <v>9.47</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="13">
         <v>10.08</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="1">
         <v>11.01</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="8">
         <v>17.07</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="9">
         <v>17.23</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="2">
         <v>17.15</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="3">
         <v>11.95</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="10">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>8.74</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="5">
         <v>8</v>
       </c>
       <c r="S2" s="11">
         <v>8.53</v>
       </c>
-      <c r="T2" s="7">
-        <v>-12.68</v>
+      <c r="T2" s="6">
+        <v>-14.22</v>
       </c>
     </row>
     <row r="3">
@@ -2024,7 +2040,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="26" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2039,41 +2055,41 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="18">
         <v>17.6</v>
       </c>
       <c r="J3" s="24">
         <v>15.99</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="19">
         <v>12.85</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="14">
         <v>9.36</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="20">
         <v>8.73</v>
       </c>
-      <c r="N3" s="14">
+      <c r="N3" s="25">
         <v>8.15</v>
       </c>
       <c r="O3" s="15">
         <v>6.67</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="21">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="18">
+      <c r="Q3" s="16">
         <v>1.21</v>
       </c>
       <c r="R3" s="22">
         <v>0.49</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="26">
         <v>2.02</v>
       </c>
-      <c r="T3" s="25">
-        <v>-15.49</v>
+      <c r="T3" s="17">
+        <v>-15.45</v>
       </c>
     </row>
     <row r="4">
@@ -2086,7 +2102,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="35" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2101,41 +2117,41 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="28">
         <v>0</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="31">
         <v>16.09</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="36">
         <v>35.27</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="32">
         <v>27.54</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="29">
         <v>14.04</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="37">
         <v>14.69</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="30">
         <v>0.26</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="39">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="33">
         <v>8.86</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="38">
         <v>11.7</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="27">
         <v>17.14</v>
       </c>
-      <c r="T4" s="36">
-        <v>-3.46</v>
+      <c r="T4" s="34">
+        <v>-5.01</v>
       </c>
     </row>
     <row r="5">
@@ -2148,7 +2164,7 @@
       <c r="C5" t="str">
         <v>600103</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -2325.72万</v>
       </c>
       <c r="E5">
@@ -2163,41 +2179,41 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="46">
         <v>7.58</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="49">
         <v>8.75</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="42">
         <v>7.87</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="50">
         <v>5.25</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="43">
         <v>5.83</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="48">
         <v>8.16</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="44">
         <v>10.5</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="51">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="47">
         <v>2.62</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="45">
         <v>4.37</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="52">
         <v>10.5</v>
       </c>
-      <c r="T5" s="44">
-        <v>37.9</v>
+      <c r="T5" s="40">
+        <v>51.6</v>
       </c>
     </row>
     <row r="6">
@@ -2210,7 +2226,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="54" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2225,41 +2241,41 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="62">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="63">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="55">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="64">
         <v>-13.5</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="56">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="57">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="59">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="58">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="60">
         <v>-18.6</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="65">
         <v>-18.95</v>
       </c>
       <c r="S6" s="53">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="57">
-        <v>18.41</v>
+      <c r="T6" s="61">
+        <v>22.88</v>
       </c>
     </row>
     <row r="7">
@@ -2272,7 +2288,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2287,33 +2303,35 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="72">
         <v>0</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="75">
         <v>2.3</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="67">
         <v>6.39</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="68">
         <v>2.05</v>
       </c>
       <c r="M7" s="69">
         <v>3.84</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="70">
         <v>9.97</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="73">
         <v>20.97</v>
       </c>
-      <c r="P7" t="str"/>
+      <c r="P7" s="66">
+        <v>32.99</v>
+      </c>
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="72">
-        <v>20.97</v>
+      <c r="T7" s="71">
+        <v>32.99</v>
       </c>
     </row>
     <row r="8">
@@ -2349,7 +2367,7 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -2375,40 +2393,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="85">
+      <c r="I9" s="77">
         <v>50</v>
       </c>
       <c r="J9" s="82">
         <v>83.33</v>
       </c>
-      <c r="K9" s="86">
+      <c r="K9" s="83">
         <v>83.33</v>
       </c>
-      <c r="L9" s="75">
+      <c r="L9" s="78">
         <v>83.33</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="79">
         <v>83.33</v>
       </c>
-      <c r="N9" s="76">
+      <c r="N9" s="85">
         <v>83.33</v>
       </c>
-      <c r="O9" s="81">
+      <c r="O9" s="86">
         <v>83.33</v>
       </c>
-      <c r="P9" s="83">
+      <c r="P9" s="84">
+        <v>83.33</v>
+      </c>
+      <c r="Q9" s="87">
         <v>80</v>
       </c>
-      <c r="Q9" s="79">
+      <c r="R9" s="76">
         <v>80</v>
       </c>
-      <c r="R9" s="77">
+      <c r="S9" s="80">
         <v>80</v>
       </c>
-      <c r="S9" s="84">
-        <v>80</v>
-      </c>
-      <c r="T9" s="80">
+      <c r="T9" s="81">
         <v>50</v>
       </c>
     </row>
@@ -2423,41 +2441,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="97">
+      <c r="I10" s="96">
         <v>5.78</v>
       </c>
-      <c r="J10" s="87">
+      <c r="J10" s="97">
         <v>6.97</v>
       </c>
-      <c r="K10" s="90">
+      <c r="K10" s="98">
         <v>10.45</v>
       </c>
-      <c r="L10" s="94">
+      <c r="L10" s="93">
         <v>7.96</v>
       </c>
-      <c r="M10" s="95">
+      <c r="M10" s="94">
         <v>5.87</v>
       </c>
-      <c r="N10" s="98">
+      <c r="N10" s="89">
         <v>7.06</v>
       </c>
-      <c r="O10" s="91">
+      <c r="O10" s="90">
         <v>5.95</v>
       </c>
-      <c r="P10" s="92">
-        <v>1.65</v>
-      </c>
-      <c r="Q10" s="88">
+      <c r="P10" s="88">
+        <v>6.87</v>
+      </c>
+      <c r="Q10" s="99">
         <v>0.57</v>
       </c>
-      <c r="R10" s="89">
+      <c r="R10" s="91">
         <v>1.12</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="92">
         <v>3.2</v>
       </c>
-      <c r="T10" s="93">
-        <v>7.61</v>
+      <c r="T10" s="95">
+        <v>12.13</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="101">
+  <fills count="104">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,13 +39,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,7 +111,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -75,31 +135,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,25 +189,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCA2C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A702F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,31 +363,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,25 +381,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,193 +453,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,54 +525,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -477,162 +543,135 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C5C9"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="100">
+  <borders count="103">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1337,7 +1376,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="103">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1634,6 +1673,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="99" fillId="100" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="100" fillId="101" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="101" fillId="102" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="102" fillId="103" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1978,7 +2026,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="1" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -1993,41 +2041,41 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="2">
         <v>9.47</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="11">
         <v>10.08</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="3">
         <v>11.01</v>
       </c>
       <c r="L2" s="8">
         <v>17.07</v>
       </c>
-      <c r="M2" s="9">
+      <c r="M2" s="7">
         <v>17.23</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="9">
         <v>17.15</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="4">
         <v>11.95</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="5">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="12">
         <v>8.74</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="6">
         <v>8</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="13">
         <v>8.53</v>
       </c>
-      <c r="T2" s="6">
-        <v>-14.22</v>
+      <c r="T2" s="10">
+        <v>-14.83</v>
       </c>
     </row>
     <row r="3">
@@ -2040,7 +2088,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="25" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2055,41 +2103,41 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="20">
         <v>17.6</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="21">
         <v>15.99</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="22">
         <v>12.85</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="17">
         <v>9.36</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="18">
         <v>8.73</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="19">
         <v>8.15</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="26">
         <v>6.67</v>
       </c>
-      <c r="P3" s="21">
+      <c r="P3" s="14">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="24">
         <v>1.21</v>
       </c>
-      <c r="R3" s="22">
+      <c r="R3" s="23">
         <v>0.49</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="15">
         <v>2.02</v>
       </c>
-      <c r="T3" s="17">
-        <v>-15.45</v>
+      <c r="T3" s="16">
+        <v>-17.02</v>
       </c>
     </row>
     <row r="4">
@@ -2102,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="39" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2117,41 +2165,41 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="36">
         <v>0</v>
       </c>
       <c r="J4" s="31">
         <v>16.09</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="28">
         <v>35.27</v>
       </c>
       <c r="L4" s="32">
         <v>27.54</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="37">
         <v>14.04</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="38">
         <v>14.69</v>
       </c>
-      <c r="O4" s="30">
+      <c r="O4" s="33">
         <v>0.26</v>
       </c>
-      <c r="P4" s="39">
+      <c r="P4" s="29">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="34">
         <v>8.86</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="27">
         <v>11.7</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="35">
         <v>17.14</v>
       </c>
-      <c r="T4" s="34">
-        <v>-5.01</v>
+      <c r="T4" s="30">
+        <v>-9.63</v>
       </c>
     </row>
     <row r="5">
@@ -2164,7 +2212,7 @@
       <c r="C5" t="str">
         <v>600103</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -2325.72万</v>
       </c>
       <c r="E5">
@@ -2179,41 +2227,41 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="43">
         <v>7.58</v>
       </c>
       <c r="J5" s="49">
         <v>8.75</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="50">
         <v>7.87</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="40">
         <v>5.25</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="41">
         <v>5.83</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="51">
         <v>8.16</v>
       </c>
-      <c r="O5" s="44">
+      <c r="O5" s="42">
         <v>10.5</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="44">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="47">
+      <c r="Q5" s="45">
         <v>2.62</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="46">
         <v>4.37</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="47">
         <v>10.5</v>
       </c>
-      <c r="T5" s="40">
-        <v>51.6</v>
+      <c r="T5" s="48">
+        <v>41.4</v>
       </c>
     </row>
     <row r="6">
@@ -2226,7 +2274,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="54" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2241,41 +2289,41 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="53">
         <v>0</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="58">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="62">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="54">
         <v>-13.5</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="55">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="59">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="63">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="60">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="56">
         <v>-18.6</v>
       </c>
       <c r="R6" s="65">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="53">
+      <c r="S6" s="61">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="61">
-        <v>22.88</v>
+      <c r="T6" s="64">
+        <v>12.77</v>
       </c>
     </row>
     <row r="7">
@@ -2288,7 +2336,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2303,35 +2351,41 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="69">
         <v>0</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="70">
         <v>2.3</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="71">
         <v>6.39</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="66">
         <v>2.05</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="67">
         <v>3.84</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="77">
         <v>9.97</v>
       </c>
       <c r="O7" s="73">
         <v>20.97</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="74">
         <v>32.99</v>
       </c>
-      <c r="Q7" t="str"/>
-      <c r="R7" t="str"/>
-      <c r="S7" t="str"/>
-      <c r="T7" s="71">
-        <v>32.99</v>
+      <c r="Q7" s="75">
+        <v>40.66</v>
+      </c>
+      <c r="R7" s="78">
+        <v>31.46</v>
+      </c>
+      <c r="S7" s="76">
+        <v>24.04</v>
+      </c>
+      <c r="T7" s="72">
+        <v>24.04</v>
       </c>
     </row>
     <row r="8">
@@ -2370,13 +2424,13 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -2393,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="77">
+      <c r="I9" s="81">
         <v>50</v>
       </c>
-      <c r="J9" s="82">
+      <c r="J9" s="86">
         <v>83.33</v>
       </c>
-      <c r="K9" s="83">
+      <c r="K9" s="84">
         <v>83.33</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="89">
         <v>83.33</v>
       </c>
-      <c r="M9" s="79">
+      <c r="M9" s="85">
         <v>83.33</v>
       </c>
-      <c r="N9" s="85">
+      <c r="N9" s="90">
         <v>83.33</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="87">
         <v>83.33</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="79">
         <v>83.33</v>
       </c>
-      <c r="Q9" s="87">
-        <v>80</v>
-      </c>
-      <c r="R9" s="76">
-        <v>80</v>
+      <c r="Q9" s="82">
+        <v>83.33</v>
+      </c>
+      <c r="R9" s="88">
+        <v>83.33</v>
       </c>
       <c r="S9" s="80">
-        <v>80</v>
-      </c>
-      <c r="T9" s="81">
+        <v>83.33</v>
+      </c>
+      <c r="T9" s="83">
         <v>50</v>
       </c>
     </row>
@@ -2441,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="96">
+      <c r="I10" s="94">
         <v>5.78</v>
       </c>
-      <c r="J10" s="97">
+      <c r="J10" s="99">
         <v>6.97</v>
       </c>
-      <c r="K10" s="98">
+      <c r="K10" s="96">
         <v>10.45</v>
       </c>
-      <c r="L10" s="93">
+      <c r="L10" s="91">
         <v>7.96</v>
       </c>
-      <c r="M10" s="94">
+      <c r="M10" s="92">
         <v>5.87</v>
       </c>
-      <c r="N10" s="89">
+      <c r="N10" s="97">
         <v>7.06</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="100">
         <v>5.95</v>
       </c>
-      <c r="P10" s="88">
+      <c r="P10" s="95">
         <v>6.87</v>
       </c>
-      <c r="Q10" s="99">
-        <v>0.57</v>
-      </c>
-      <c r="R10" s="91">
-        <v>1.12</v>
-      </c>
-      <c r="S10" s="92">
-        <v>3.2</v>
-      </c>
-      <c r="T10" s="95">
-        <v>12.13</v>
+      <c r="Q10" s="101">
+        <v>7.25</v>
+      </c>
+      <c r="R10" s="93">
+        <v>6.18</v>
+      </c>
+      <c r="S10" s="102">
+        <v>6.68</v>
+      </c>
+      <c r="T10" s="98">
+        <v>6.12</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -39,18 +39,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -69,25 +105,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB42330"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,6 +117,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -111,19 +195,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8538"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,49 +357,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,61 +417,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A702F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -255,97 +483,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,283 +555,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -2041,28 +2041,28 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="1">
         <v>9.47</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="2">
         <v>10.08</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="9">
         <v>11.01</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="3">
         <v>17.07</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="5">
         <v>17.23</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="10">
         <v>17.15</v>
       </c>
       <c r="O2" s="4">
         <v>11.95</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="11">
         <v>9.67</v>
       </c>
       <c r="Q2" s="12">
@@ -2071,11 +2071,11 @@
       <c r="R2" s="6">
         <v>8</v>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="7">
         <v>8.53</v>
       </c>
-      <c r="T2" s="10">
-        <v>-14.83</v>
+      <c r="T2" s="13">
+        <v>-18.41</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="16">
         <v>17.6</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="17">
         <v>15.99</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="25">
         <v>12.85</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="18">
         <v>9.36</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="26">
         <v>8.73</v>
       </c>
       <c r="N3" s="19">
         <v>8.15</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="20">
         <v>6.67</v>
       </c>
       <c r="P3" s="14">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="21">
         <v>1.21</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="15">
         <v>0.49</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="22">
         <v>2.02</v>
       </c>
-      <c r="T3" s="16">
-        <v>-17.02</v>
+      <c r="T3" s="23">
+        <v>-23.87</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="33" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="34">
         <v>0</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="28">
         <v>16.09</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="29">
         <v>35.27</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="30">
         <v>27.54</v>
       </c>
       <c r="M4" s="37">
         <v>14.04</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="35">
         <v>14.69</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="38">
         <v>0.26</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="31">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="39">
         <v>8.86</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="32">
         <v>11.7</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="27">
         <v>17.14</v>
       </c>
-      <c r="T4" s="30">
-        <v>-9.63</v>
+      <c r="T4" s="36">
+        <v>-7.8</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>600103</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="41" t="str">
         <v>净卖: -2325.72万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="52">
         <v>7.58</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="47">
         <v>8.75</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="40">
         <v>7.87</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="48">
         <v>5.25</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="50">
         <v>5.83</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="49">
         <v>8.16</v>
       </c>
       <c r="O5" s="42">
         <v>10.5</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="43">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="44">
         <v>2.62</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="45">
         <v>4.37</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="51">
         <v>10.5</v>
       </c>
-      <c r="T5" s="48">
-        <v>41.4</v>
+      <c r="T5" s="46">
+        <v>38.48</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="53">
+      <c r="I6" s="60">
         <v>0</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="61">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="62">
+      <c r="K6" s="56">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="57">
         <v>-13.5</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="65">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="64">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="58">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="62">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="53">
         <v>-18.6</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="54">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="59">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="64">
-        <v>12.77</v>
+      <c r="T6" s="55">
+        <v>12.01</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="73" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="74">
         <v>0</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="75">
         <v>2.3</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="68">
         <v>6.39</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="70">
         <v>2.05</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="76">
         <v>3.84</v>
       </c>
       <c r="N7" s="77">
         <v>9.97</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="71">
         <v>20.97</v>
       </c>
-      <c r="P7" s="74">
+      <c r="P7" s="78">
         <v>32.99</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="69">
         <v>40.66</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="72">
         <v>31.46</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="66">
         <v>24.04</v>
       </c>
-      <c r="T7" s="72">
-        <v>24.04</v>
+      <c r="T7" s="67">
+        <v>21.48</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="81">
+      <c r="I9" s="87">
         <v>50</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="85">
         <v>83.33</v>
       </c>
-      <c r="K9" s="84">
+      <c r="K9" s="81">
         <v>83.33</v>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="82">
         <v>83.33</v>
       </c>
-      <c r="M9" s="85">
+      <c r="M9" s="83">
         <v>83.33</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="88">
         <v>83.33</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="89">
         <v>83.33</v>
       </c>
-      <c r="P9" s="79">
+      <c r="P9" s="84">
         <v>83.33</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="90">
         <v>83.33</v>
       </c>
-      <c r="R9" s="88">
+      <c r="R9" s="79">
         <v>83.33</v>
       </c>
       <c r="S9" s="80">
         <v>83.33</v>
       </c>
-      <c r="T9" s="83">
+      <c r="T9" s="86">
         <v>50</v>
       </c>
     </row>
@@ -2498,38 +2498,38 @@
       <c r="I10" s="94">
         <v>5.78</v>
       </c>
-      <c r="J10" s="99">
+      <c r="J10" s="101">
         <v>6.97</v>
       </c>
-      <c r="K10" s="96">
+      <c r="K10" s="102">
         <v>10.45</v>
       </c>
-      <c r="L10" s="91">
+      <c r="L10" s="96">
         <v>7.96</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="93">
         <v>5.87</v>
       </c>
       <c r="N10" s="97">
         <v>7.06</v>
       </c>
-      <c r="O10" s="100">
+      <c r="O10" s="91">
         <v>5.95</v>
       </c>
       <c r="P10" s="95">
         <v>6.87</v>
       </c>
-      <c r="Q10" s="101">
+      <c r="Q10" s="98">
         <v>7.25</v>
       </c>
-      <c r="R10" s="93">
+      <c r="R10" s="92">
         <v>6.18</v>
       </c>
-      <c r="S10" s="102">
+      <c r="S10" s="99">
         <v>6.68</v>
       </c>
-      <c r="T10" s="98">
-        <v>6.12</v>
+      <c r="T10" s="100">
+        <v>3.65</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/Asking/index.xlsx
+++ b/youzi/Asking/index.xlsx
@@ -39,6 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAC1F2C"/>
         <bgColor/>
       </patternFill>
@@ -51,31 +117,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
+        <fgColor rgb="FFFBEBEC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,13 +147,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
+        <fgColor rgb="FFAD202D"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,37 +159,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4636F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CED1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77882"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB32230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4636F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD202D"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,19 +345,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCA2C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CED1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
+        <fgColor rgb="FFE04E5C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,49 +357,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77882"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,6 +459,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEA2A9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -249,145 +543,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F8538"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -399,241 +573,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEEA2A9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED98A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2026,7 +2026,7 @@
       <c r="C2" t="str">
         <v>000997</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -2811.23万</v>
       </c>
       <c r="E2">
@@ -2041,31 +2041,31 @@
       <c r="H2">
         <v>0.49</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="12">
         <v>9.47</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="8">
         <v>10.08</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="1">
         <v>11.01</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="13">
         <v>17.07</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>17.23</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="3">
         <v>17.15</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="9">
         <v>11.95</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="5">
         <v>9.67</v>
       </c>
-      <c r="Q2" s="12">
+      <c r="Q2" s="10">
         <v>8.74</v>
       </c>
       <c r="R2" s="6">
@@ -2074,8 +2074,8 @@
       <c r="S2" s="7">
         <v>8.53</v>
       </c>
-      <c r="T2" s="13">
-        <v>-18.41</v>
+      <c r="T2" s="4">
+        <v>-19.59</v>
       </c>
     </row>
     <row r="3">
@@ -2088,7 +2088,7 @@
       <c r="C3" t="str">
         <v>301151</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="17" t="str">
         <v>净卖: -997.36万</v>
       </c>
       <c r="E3">
@@ -2103,41 +2103,41 @@
       <c r="H3">
         <v>2.06</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="21">
         <v>17.6</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="18">
         <v>15.99</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="23">
         <v>12.85</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="19">
         <v>9.36</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="20">
         <v>8.73</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="24">
         <v>8.15</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="15">
         <v>6.67</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="25">
         <v>3.85</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="26">
         <v>1.21</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="14">
         <v>0.49</v>
       </c>
       <c r="S3" s="22">
         <v>2.02</v>
       </c>
-      <c r="T3" s="23">
-        <v>-23.87</v>
+      <c r="T3" s="16">
+        <v>-22.97</v>
       </c>
     </row>
     <row r="4">
@@ -2150,7 +2150,7 @@
       <c r="C4" t="str">
         <v>688228</v>
       </c>
-      <c r="D4" s="33" t="str">
+      <c r="D4" s="37" t="str">
         <v>净卖: -1502.97万</v>
       </c>
       <c r="E4">
@@ -2165,41 +2165,41 @@
       <c r="H4">
         <v>20</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="35">
         <v>0</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="38">
         <v>16.09</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>35.27</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>27.54</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="28">
         <v>14.04</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="32">
         <v>14.69</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="39">
         <v>0.26</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="27">
         <v>3.34</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="33">
         <v>8.86</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="34">
         <v>11.7</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="29">
         <v>17.14</v>
       </c>
       <c r="T4" s="36">
-        <v>-7.8</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="5">
@@ -2212,7 +2212,7 @@
       <c r="C5" t="str">
         <v>600103</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -2325.72万</v>
       </c>
       <c r="E5">
@@ -2227,41 +2227,41 @@
       <c r="H5">
         <v>2.39</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="44">
         <v>7.58</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="49">
         <v>8.75</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="45">
         <v>7.87</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="47">
         <v>5.25</v>
       </c>
       <c r="M5" s="50">
         <v>5.83</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="51">
         <v>8.16</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="41">
         <v>10.5</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="42">
         <v>7.87</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="43">
         <v>2.62</v>
       </c>
-      <c r="R5" s="45">
+      <c r="R5" s="52">
         <v>4.37</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="48">
         <v>10.5</v>
       </c>
-      <c r="T5" s="46">
-        <v>38.48</v>
+      <c r="T5" s="40">
+        <v>32.36</v>
       </c>
     </row>
     <row r="6">
@@ -2274,7 +2274,7 @@
       <c r="C6" t="str">
         <v>301181</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="59" t="str">
         <v>净卖: -446.18万</v>
       </c>
       <c r="E6">
@@ -2289,41 +2289,41 @@
       <c r="H6">
         <v>-20</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="61">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="62">
         <v>-11.38</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="63">
         <v>-10.72</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="65">
         <v>-13.5</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="64">
         <v>-14.45</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="53">
         <v>-15.75</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="54">
         <v>-14.62</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="55">
         <v>-16.5</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="57">
         <v>-18.6</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="56">
         <v>-18.95</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="60">
         <v>-22.17</v>
       </c>
-      <c r="T6" s="55">
-        <v>12.01</v>
+      <c r="T6" s="58">
+        <v>12.43</v>
       </c>
     </row>
     <row r="7">
@@ -2336,7 +2336,7 @@
       <c r="C7" t="str">
         <v>600103</v>
       </c>
-      <c r="D7" s="73" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -796.78万</v>
       </c>
       <c r="E7">
@@ -2351,41 +2351,41 @@
       <c r="H7">
         <v>10.14</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="66">
         <v>0</v>
       </c>
       <c r="J7" s="75">
         <v>2.3</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="71">
         <v>6.39</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="72">
         <v>2.05</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="67">
         <v>3.84</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="73">
         <v>9.97</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="76">
         <v>20.97</v>
       </c>
-      <c r="P7" s="78">
+      <c r="P7" s="77">
         <v>32.99</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="68">
         <v>40.66</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="78">
         <v>31.46</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="69">
         <v>24.04</v>
       </c>
-      <c r="T7" s="67">
-        <v>21.48</v>
+      <c r="T7" s="74">
+        <v>16.11</v>
       </c>
     </row>
     <row r="8">
@@ -2447,40 +2447,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="87">
+      <c r="I9" s="83">
         <v>50</v>
       </c>
-      <c r="J9" s="85">
+      <c r="J9" s="87">
         <v>83.33</v>
       </c>
-      <c r="K9" s="81">
+      <c r="K9" s="90">
         <v>83.33</v>
       </c>
-      <c r="L9" s="82">
+      <c r="L9" s="84">
         <v>83.33</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="86">
         <v>83.33</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="79">
         <v>83.33</v>
       </c>
-      <c r="O9" s="89">
+      <c r="O9" s="85">
         <v>83.33</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="88">
         <v>83.33</v>
       </c>
-      <c r="Q9" s="90">
+      <c r="Q9" s="80">
         <v>83.33</v>
       </c>
-      <c r="R9" s="79">
+      <c r="R9" s="81">
         <v>83.33</v>
       </c>
-      <c r="S9" s="80">
+      <c r="S9" s="82">
         <v>83.33</v>
       </c>
-      <c r="T9" s="86">
+      <c r="T9" s="89">
         <v>50</v>
       </c>
     </row>
@@ -2495,41 +2495,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="94">
+      <c r="I10" s="95">
         <v>5.78</v>
       </c>
-      <c r="J10" s="101">
+      <c r="J10" s="100">
         <v>6.97</v>
       </c>
-      <c r="K10" s="102">
+      <c r="K10" s="96">
         <v>10.45</v>
       </c>
-      <c r="L10" s="96">
+      <c r="L10" s="97">
         <v>7.96</v>
       </c>
       <c r="M10" s="93">
         <v>5.87</v>
       </c>
-      <c r="N10" s="97">
+      <c r="N10" s="94">
         <v>7.06</v>
       </c>
-      <c r="O10" s="91">
+      <c r="O10" s="92">
         <v>5.95</v>
       </c>
-      <c r="P10" s="95">
+      <c r="P10" s="98">
         <v>6.87</v>
       </c>
-      <c r="Q10" s="98">
+      <c r="Q10" s="101">
         <v>7.25</v>
       </c>
-      <c r="R10" s="92">
+      <c r="R10" s="102">
         <v>6.18</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="91">
         <v>6.68</v>
       </c>
-      <c r="T10" s="100">
-        <v>3.65</v>
+      <c r="T10" s="99">
+        <v>1.01</v>
       </c>
     </row>
   </sheetData>
